--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/25 12:28:53</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18181.82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>lh_xxxx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/25 11:26:04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>8199</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>970.3</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>lh_zzzz</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>8199</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>158199</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19152.11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>970.3</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19152.11</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/25 12:28:53</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18181.82</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lh_xxxx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>09/25 11:26:04</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>8199</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>970.3</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>lh_zzzz</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>158199</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19152.11</t>
+          <t>268199</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32485.45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>19152.11</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>32485.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>09/25 13:18:04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>268199</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32485.45</t>
+          <t>268199</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32485.45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>32485.45</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14485.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-2026-09-25.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/25 14:51:25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14484</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/25 13:18:04</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>18000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>268199</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32485.45</t>
+          <t>268199</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>32485.45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>32484</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>14485.45</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.45</t>
         </is>
       </c>
     </row>
